--- a/data/trans_dic/IMC_inf_MED_R3-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IMC_inf_MED_R3-Habitat-trans_dic.xlsx
@@ -532,7 +532,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,31 +632,31 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.2752347056598735</v>
+        <v>0.2613056455159087</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.2538348872542642</v>
+        <v>0.2488368451767389</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.1628078487210226</v>
+        <v>0.1501657544313318</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.2046747431889658</v>
+        <v>0.2044448283171116</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.1817679277948809</v>
+        <v>0.1526254830569309</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.1763872696218786</v>
+        <v>0.1765523073340925</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.2412883454912537</v>
+        <v>0.2336469529135845</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.2199838917519235</v>
+        <v>0.2036196312292379</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.1686467967774625</v>
+        <v>0.1614219616634998</v>
       </c>
     </row>
     <row r="5">
@@ -667,31 +667,31 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.2057908214184196</v>
+        <v>0.1973697962227036</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.1775313714067839</v>
+        <v>0.1833811816685801</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.09087570539703239</v>
+        <v>0.08486706155624626</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.1413213526852495</v>
+        <v>0.1481628009099949</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.1197959042203699</v>
+        <v>0.1016456079143461</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.1027806572795444</v>
+        <v>0.1115411120293201</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.1926481207837508</v>
+        <v>0.18612334548887</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1713324592961707</v>
+        <v>0.1574184348924109</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.1146736692301491</v>
+        <v>0.1141010686034348</v>
       </c>
     </row>
     <row r="6">
@@ -702,31 +702,31 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3615975711589391</v>
+        <v>0.329538402012035</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.3272251251342345</v>
+        <v>0.3255462836979782</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.2606965003658003</v>
+        <v>0.2339029829249665</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.2850670512574741</v>
+        <v>0.2750031447051366</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.2535513365395959</v>
+        <v>0.2141018342013256</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.2655659328987141</v>
+        <v>0.2689483325178085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.2956047569235727</v>
+        <v>0.2809224560448552</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.2761729036409807</v>
+        <v>0.2524808520210873</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.2369527101255318</v>
+        <v>0.2231010663123101</v>
       </c>
     </row>
     <row r="7">
@@ -741,31 +741,31 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.290713859436301</v>
+        <v>0.2753435814424476</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.1977818168628815</v>
+        <v>0.1894535274969908</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.2748768958839828</v>
+        <v>0.2643688460722937</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.1931891921492553</v>
+        <v>0.1740566249681697</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.09622309773472168</v>
+        <v>0.08632514459450479</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.09680144018010524</v>
+        <v>0.1014056134887852</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.2440985989810878</v>
+        <v>0.2263534100329646</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.1481892152270589</v>
+        <v>0.1396265659548196</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.204806662560819</v>
+        <v>0.2003175481456796</v>
       </c>
     </row>
     <row r="8">
@@ -776,31 +776,31 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.2349356613988266</v>
+        <v>0.2279448856086548</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.147343673179929</v>
+        <v>0.146058449363798</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.2015016787517532</v>
+        <v>0.1966236251241392</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.1434599216248312</v>
+        <v>0.1293149302292214</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0630466988890159</v>
+        <v>0.05905927657683503</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.04886045880550173</v>
+        <v>0.05569669935410285</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.2059371317560255</v>
+        <v>0.1921840175754167</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1158705527965619</v>
+        <v>0.1108238491333943</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.1543194423839029</v>
+        <v>0.1503440891866217</v>
       </c>
     </row>
     <row r="9">
@@ -811,31 +811,31 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.3479940415037269</v>
+        <v>0.3329603822313933</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.2585453694158905</v>
+        <v>0.2355988730451591</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.3613011859633695</v>
+        <v>0.3458255254449055</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.2474857912316754</v>
+        <v>0.2201484719254582</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.1370908864245823</v>
+        <v>0.1242200532268501</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.1627288079883664</v>
+        <v>0.1718426728951018</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.2878397666728519</v>
+        <v>0.2648693265837439</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.1803643291353104</v>
+        <v>0.170504431623779</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.2648452985617089</v>
+        <v>0.2592903548121479</v>
       </c>
     </row>
     <row r="10">
@@ -850,31 +850,31 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3144234728537287</v>
+        <v>0.2687301828292754</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.2194124222232425</v>
+        <v>0.2047055141698135</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.1347476497140789</v>
+        <v>0.1329000773951174</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.2609939366374045</v>
+        <v>0.260228438382454</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1558654007583933</v>
+        <v>0.1524169014244255</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.1029984318363002</v>
+        <v>0.1118344033379354</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.2877874994527754</v>
+        <v>0.2645919951558334</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.1887213606740852</v>
+        <v>0.1798651859263506</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.1207424290484769</v>
+        <v>0.123403923220963</v>
       </c>
     </row>
     <row r="11">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.2465483254164111</v>
+        <v>0.210119618609821</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.1618967560998067</v>
+        <v>0.1508286511736709</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.07503596769755208</v>
+        <v>0.07277751834411275</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.2020111754259791</v>
+        <v>0.2061137524436332</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1100274645555025</v>
+        <v>0.1116624329292148</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.04865427529400162</v>
+        <v>0.05619206950237457</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.2398740915463062</v>
+        <v>0.2229537546672978</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.1489179455000354</v>
+        <v>0.1473979636030185</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.07960238495621767</v>
+        <v>0.08048995194240094</v>
       </c>
     </row>
     <row r="12">
@@ -920,31 +920,31 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.3891153984198059</v>
+        <v>0.3297297399807297</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.292196314948622</v>
+        <v>0.2641086438684956</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.2266253153534721</v>
+        <v>0.2160921128857028</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3319454431499489</v>
+        <v>0.3239659864158266</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.2137120429069426</v>
+        <v>0.2018321090449888</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.1931199478039745</v>
+        <v>0.2081445025068331</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.3364723859118982</v>
+        <v>0.3054801618904923</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.230164400395785</v>
+        <v>0.2193847351988305</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.1856407848390035</v>
+        <v>0.1804501261012085</v>
       </c>
     </row>
     <row r="13">
@@ -959,31 +959,31 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.2476886683391901</v>
+        <v>0.2294736351804926</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.2030429839154171</v>
+        <v>0.1832583655702018</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.1801421257669336</v>
+        <v>0.1741108295623653</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.2177774456903336</v>
+        <v>0.2139910702057938</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1446337279445108</v>
+        <v>0.1362121907993306</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.1130189512732475</v>
+        <v>0.107065888588577</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.2327925632155271</v>
+        <v>0.2218201596193866</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.1749214350456013</v>
+        <v>0.1607113871461449</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.1452735441782525</v>
+        <v>0.1395641841459052</v>
       </c>
     </row>
     <row r="14">
@@ -994,31 +994,31 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.1887269081052286</v>
+        <v>0.174279532518029</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.1515149538568964</v>
+        <v>0.1390260228456632</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.1064203895967125</v>
+        <v>0.1083313772914528</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1656850046235661</v>
+        <v>0.1641208479188266</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.09786918359538173</v>
+        <v>0.09420270419203386</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.06030540055374781</v>
+        <v>0.05990259099516628</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.1901879396984232</v>
+        <v>0.1841878564024108</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.141117372477677</v>
+        <v>0.1275055180551756</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.09998708732044541</v>
+        <v>0.09599716070713873</v>
       </c>
     </row>
     <row r="15">
@@ -1029,31 +1029,31 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.3131993815877711</v>
+        <v>0.2832273822579972</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.2615479211337577</v>
+        <v>0.2367304545757065</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.2827013419578314</v>
+        <v>0.2699092625989247</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.2855174001253332</v>
+        <v>0.2727073663301839</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.200776700183377</v>
+        <v>0.1821766096305082</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.1839983610626894</v>
+        <v>0.1796416875417758</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.2726675212123678</v>
+        <v>0.2644018780861013</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.2150621712038234</v>
+        <v>0.1933425532969534</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.2105683256926536</v>
+        <v>0.1986286432802566</v>
       </c>
     </row>
     <row r="16">
@@ -1068,31 +1068,31 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2807150773981362</v>
+        <v>0.2584946618186473</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.2147325958129284</v>
+        <v>0.2026631501550434</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.199577453218781</v>
+        <v>0.1916390354652999</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.218121588944378</v>
+        <v>0.2102289689071407</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1391908963230728</v>
+        <v>0.128250271495198</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.1170031953429169</v>
+        <v>0.1187915259234743</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.2501080246998801</v>
+        <v>0.2349478947396191</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.1783443098308589</v>
+        <v>0.167118795285524</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.16288063728964</v>
+        <v>0.1592113937317494</v>
       </c>
     </row>
     <row r="17">
@@ -1103,31 +1103,31 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.2507700043450333</v>
+        <v>0.2308892092994714</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1870940664698035</v>
+        <v>0.176747335080706</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1610977255455545</v>
+        <v>0.1558067116395825</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1890184602461841</v>
+        <v>0.1842705667851912</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1175470932371663</v>
+        <v>0.10599752830818</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.0877790334129884</v>
+        <v>0.08870829937120299</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.2285624377737537</v>
+        <v>0.214265771825843</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.159939460990371</v>
+        <v>0.1504129073899769</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.1398170843121347</v>
+        <v>0.136264711853671</v>
       </c>
     </row>
     <row r="18">
@@ -1138,31 +1138,31 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3141416914663673</v>
+        <v>0.2887002357744994</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.2481324942288383</v>
+        <v>0.2290646092616782</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.2475552608383892</v>
+        <v>0.2365777460481445</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.2487304796293391</v>
+        <v>0.2393603117884866</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1691366455307075</v>
+        <v>0.1502560382600164</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.153483405076763</v>
+        <v>0.1557822107223183</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.2729750716981049</v>
+        <v>0.2553922250896048</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.1994719594363856</v>
+        <v>0.1855186742623794</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.1967909768119987</v>
+        <v>0.1891680988468435</v>
       </c>
     </row>
     <row r="19">
@@ -1213,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 71,23%)</t>
+          <t>Menores según si tienen obesidad u obesidad intensa, IMC medido (tasa de respuesta: 79,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1313,31 +1313,31 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1348,31 +1348,31 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>28073</v>
+        <v>33156</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>24922</v>
+        <v>30220</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>8815</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>19355</v>
+        <v>24570</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>15808</v>
+        <v>16436</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>7204</v>
+        <v>7710</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>47428</v>
+        <v>57725</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>40730</v>
+        <v>46656</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>16018</v>
+        <v>16524</v>
       </c>
     </row>
     <row r="6">
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>20990</v>
+        <v>25043</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>17430</v>
+        <v>22271</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>4920</v>
+        <v>4982</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>13364</v>
+        <v>17806</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>10418</v>
+        <v>10946</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>4198</v>
+        <v>4871</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>37867</v>
+        <v>45984</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>31722</v>
+        <v>36070</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>10892</v>
+        <v>11680</v>
       </c>
     </row>
     <row r="7">
@@ -1418,31 +1418,31 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>36882</v>
+        <v>41813</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>32127</v>
+        <v>39536</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>14114</v>
+        <v>13730</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>26958</v>
+        <v>33049</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>22051</v>
+        <v>23056</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>10846</v>
+        <v>11745</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>58105</v>
+        <v>69405</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>51133</v>
+        <v>57851</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>22506</v>
+        <v>22838</v>
       </c>
     </row>
     <row r="8">
@@ -1457,31 +1457,31 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>42</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>45765</v>
+        <v>52408</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>30538</v>
+        <v>34630</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>28583</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>27847</v>
+        <v>31034</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>14178</v>
+        <v>14751</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>6530</v>
+        <v>7100</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>73612</v>
+        <v>83442</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>44716</v>
+        <v>49381</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>35113</v>
+        <v>35682</v>
       </c>
     </row>
     <row r="10">
@@ -1527,31 +1527,31 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>36984</v>
+        <v>43386</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22750</v>
+        <v>26698</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>20953</v>
+        <v>21258</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>20679</v>
+        <v>23057</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>9290</v>
+        <v>10092</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3296</v>
+        <v>3899</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>62104</v>
+        <v>70846</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>34964</v>
+        <v>39195</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>26457</v>
+        <v>26780</v>
       </c>
     </row>
     <row r="11">
@@ -1562,31 +1562,31 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>54782</v>
+        <v>63374</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>39919</v>
+        <v>43065</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>37569</v>
+        <v>37390</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>35674</v>
+        <v>39253</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>20200</v>
+        <v>21226</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>10978</v>
+        <v>12031</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>86803</v>
+        <v>97640</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>54425</v>
+        <v>60302</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>45406</v>
+        <v>46187</v>
       </c>
     </row>
     <row r="12">
@@ -1601,31 +1601,31 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>14</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>36268</v>
+        <v>36922</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>26184</v>
+        <v>30138</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>9418</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>29928</v>
+        <v>33908</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>17375</v>
+        <v>20307</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>5682</v>
+        <v>6505</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>66197</v>
+        <v>70830</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>43558</v>
+        <v>50445</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>15100</v>
+        <v>15923</v>
       </c>
     </row>
     <row r="14">
@@ -1671,31 +1671,31 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>28439</v>
+        <v>28869</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>19320</v>
+        <v>22206</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>5245</v>
+        <v>5157</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>23165</v>
+        <v>26856</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>12265</v>
+        <v>14877</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>2684</v>
+        <v>3268</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>55176</v>
+        <v>59683</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>34371</v>
+        <v>41339</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>9955</v>
+        <v>10386</v>
       </c>
     </row>
     <row r="15">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>44884</v>
+        <v>45303</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>34870</v>
+        <v>38883</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>15840</v>
+        <v>15314</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>38064</v>
+        <v>42212</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>23823</v>
+        <v>26891</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>10654</v>
+        <v>12107</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>77395</v>
+        <v>81775</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>53124</v>
+        <v>61529</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>23216</v>
+        <v>23284</v>
       </c>
     </row>
     <row r="16">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H16" s="6" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -1780,31 +1780,31 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>36773</v>
+        <v>39298</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>30924</v>
+        <v>32994</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>12123</v>
+        <v>12578</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>32076</v>
+        <v>35824</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>20453</v>
+        <v>22570</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>8222</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>68849</v>
+        <v>75122</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>51377</v>
+        <v>55563</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>20345</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="18">
@@ -1815,31 +1815,31 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>28020</v>
+        <v>29846</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>23076</v>
+        <v>25030</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>7162</v>
+        <v>7826</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>24404</v>
+        <v>27476</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>13840</v>
+        <v>15609</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>4387</v>
+        <v>4600</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>56249</v>
+        <v>62378</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>41448</v>
+        <v>44083</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>14003</v>
+        <v>14307</v>
       </c>
     </row>
     <row r="19">
@@ -1850,31 +1850,31 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>46499</v>
+        <v>48503</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>39835</v>
+        <v>42621</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>19025</v>
+        <v>19499</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>42054</v>
+        <v>45654</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>28392</v>
+        <v>30186</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>13386</v>
+        <v>13796</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>80643</v>
+        <v>89543</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>63167</v>
+        <v>66845</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>29489</v>
+        <v>29603</v>
       </c>
     </row>
     <row r="20">
@@ -1889,31 +1889,31 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
@@ -1924,31 +1924,31 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>146880</v>
+        <v>161783</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>112567</v>
+        <v>127982</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>58938</v>
+        <v>59393</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>109207</v>
+        <v>125336</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>67814</v>
+        <v>74064</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>27638</v>
+        <v>29537</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>256087</v>
+        <v>287119</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>180381</v>
+        <v>202045</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>86577</v>
+        <v>88930</v>
       </c>
     </row>
     <row r="22">
@@ -1959,31 +1959,31 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>131211</v>
+        <v>144506</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>98079</v>
+        <v>111616</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>47575</v>
+        <v>48288</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>94636</v>
+        <v>109860</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>57269</v>
+        <v>61213</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>20735</v>
+        <v>22057</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>234026</v>
+        <v>261844</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>161766</v>
+        <v>181848</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>74318</v>
+        <v>76113</v>
       </c>
     </row>
     <row r="23">
@@ -1994,31 +1994,31 @@
         </is>
       </c>
       <c r="C23" s="6" t="n">
-        <v>164370</v>
+        <v>180688</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>130076</v>
+        <v>144654</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>73107</v>
+        <v>73321</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>124532</v>
+        <v>142704</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>82403</v>
+        <v>86772</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>36256</v>
+        <v>38734</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>279500</v>
+        <v>312103</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>201750</v>
+        <v>224291</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>104601</v>
+        <v>105663</v>
       </c>
     </row>
     <row r="24">
